--- a/make_table/tuikuan/tuihuo_table.xlsx
+++ b/make_table/tuikuan/tuihuo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05月02日</t>
+          <t>05月15日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5111094925001027547</t>
+          <t>3300739898551029157</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tb942192175</t>
+          <t>马勇山</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50g清香鸭屎*1，7g清香桂花*1，完好</t>
+          <t>庄园东方红50g*1，完好</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>JT3161329705289</t>
+          <t>772062536610159</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>110</v>
+        <v>140.2</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05月02日</t>
+          <t>05月15日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,18 +545,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3298624789787020998</t>
+          <t>5115377736942050732</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>快乐兔子999200</t>
+          <t>bffymyq</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>200g老丛私房凹富后*1，50g庄园蜜兰*1，50g庄园鸭屎*1，羊脂玉茶具公道杯*1，完好</t>
+          <t>庄园鸭屎50g*1，完好</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,11 +571,60 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SF0223964041105</t>
+          <t>772062540631547</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1919.67</v>
+        <v>138.32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>05月15日</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5114123499802013647</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>maartenigel</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>庄园蜜兰50g*1，崬顶蜜兰50g*1，庄园东方红50g*1，庄园锯朵仔50g*1，清香桂花50g*1，庄园鸭屎50g*1，以上完好</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>退货</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>772062623195575</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>769.21</v>
       </c>
     </row>
   </sheetData>

--- a/make_table/tuikuan/tuihuo_table.xlsx
+++ b/make_table/tuikuan/tuihuo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05月15日</t>
+          <t>05月22日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3300739898551029157</t>
+          <t>5116134240360002301</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>马勇山</t>
+          <t>淘taohuo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>庄园东方红50g*1，完好</t>
+          <t>金香鸭屎50g*1，岽顶蜜兰50g*1，完好</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>772062536610159</t>
+          <t>73709362752445</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>140.2</v>
+        <v>219.6</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05月15日</t>
+          <t>05月22日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,18 +545,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5115377736942050732</t>
+          <t>5115783207060025631</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>bffymyq</t>
+          <t>carol534211043</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>庄园鸭屎50g*1，完好</t>
+          <t>6大（2.0）组合装50g*6，完好</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,60 +571,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>772062540631547</t>
+          <t>772063611779312</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>138.32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>05月15日</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>天猫</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5114123499802013647</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>maartenigel</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>庄园蜜兰50g*1，崬顶蜜兰50g*1，庄园东方红50g*1，庄园锯朵仔50g*1，清香桂花50g*1，庄园鸭屎50g*1，以上完好</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>退货</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>口感不合适</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>772062623195575</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>769.21</v>
+        <v>774.21</v>
       </c>
     </row>
   </sheetData>

--- a/make_table/tuikuan/tuihuo_table.xlsx
+++ b/make_table/tuikuan/tuihuo_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05月22日</t>
+          <t>06月26日</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,18 +496,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5116134240360002301</t>
+          <t>5120377599274061707</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>淘taohuo</t>
+          <t>tb237377026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>金香鸭屎50g*1，岽顶蜜兰50g*1，完好</t>
+          <t>金香鸭屎50g*1，完好</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -522,11 +522,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>73709362752445</t>
+          <t>631154016405149</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>219.6</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05月22日</t>
+          <t>06月26日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -545,37 +545,86 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5115783207060025631</t>
+          <t>5120768017542016448</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>carol534211043</t>
+          <t>xzj8286</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6大（2.0）组合装50g*6，完好</t>
+          <t>庄园蜜兰50g*1，完好，盒损</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>换货</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>口感不合适</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SF5194799481055</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06月26日</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>天猫</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5120771292895032318</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>dddbbbjjjqwe</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>岽顶蜜兰252g*1，完好</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>退货</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>口感不合适</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>772063611779312</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>774.21</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>73714311762221</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
